--- a/LangMod/EN/Dialog/Drama/RQXDIalog.xlsx
+++ b/LangMod/EN/Dialog/Drama/RQXDIalog.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="112">
   <si>
     <t xml:space="preserve">step</t>
   </si>
@@ -31,6 +31,9 @@
     <t xml:space="preserve">if</t>
   </si>
   <si>
+    <t xml:space="preserve">if2</t>
+  </si>
+  <si>
     <t xml:space="preserve">action</t>
   </si>
   <si>
@@ -76,20 +79,651 @@
     <t xml:space="preserve">end</t>
   </si>
   <si>
-    <t xml:space="preserve">assassin</t>
+    <t xml:space="preserve">assassin_MG_nonego_1_main</t>
   </si>
   <si>
     <t xml:space="preserve">待て！</t>
   </si>
   <si>
-    <t xml:space="preserve">冒険者は通す！ペットも通す{よ}！
-…#1は通さない！
-そいつだけは死んでもら{う}！覚悟して{くれ}！</t>
-  </si>
-  <si>
-    <t xml:space="preserve">冒険者は通す！ペットも通す{よ}！
-…#1は通さ{ない}！
-そいつだけは死んでもら{う}！覚悟して{くれ}！</t>
+    <t xml:space="preserve">HALT!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">護衛の依頼を受けた冒険者{だな}？
+そこの&lt;color=green&gt;#1&lt;/color&gt;の首には、賞金がかかっている{のだ}。
+{YOU}に恨みはない{が}、諸共くたばってもらう{よ}！
+いく{よ}！</t>
+  </si>
+  <si>
+    <t xml:space="preserve">You’re the adventurer, who accepted the escort job right?
+There’s a bounty on &lt;color=green&gt;#1&lt;/color&gt;’s head.
+I’ve got nothing against you, but you’re going down with him!
+Here we go!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">setFlag</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RQX_negoaccept,0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RQX_negoraise,0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">endwithcallback</t>
+  </si>
+  <si>
+    <t xml:space="preserve">assassin_MG_nego_1_main</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{YOU}！そこの冒険者！待って{くれ}！</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yo! Hey, adventurer! Wait for me!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{I}は&lt;color=green&gt;#1&lt;/color&gt;を捕まえる依頼を受けた{のだ}。
+{だが}、{YOU}のような奴が関わっているとは聞いていなかった{よ}。
+なるべく暴力は無しでいきたい{よ}、
+&lt;color=green&gt;#2&lt;/color&gt;をやるから、ここは譲ってくれない{か}？</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">I was hired to capture &lt;color=green&gt;#1&lt;/color&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">. But I wasn't told that someone like you would be involved.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">I'd rather avoid a fight if possible.
+I'll give you &lt;color=green&gt;#2&lt;/color&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, so how about you walk away and let this go?</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">assassin_MG_nego_1_refuse</t>
+  </si>
+  <si>
+    <t xml:space="preserve">choice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">お断りだ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No way.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">assassin_MG_nego_1_accept</t>
+  </si>
+  <si>
+    <t xml:space="preserve">いいよ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I accept.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">assassin_MG_nego_1_raise</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&gt;=,RQX_canraise,1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">それでは安すぎる</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gimme more!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">assassin_MG_nego_1_bust</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;,RQX_canraise,1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">残念{だな}。
+では仕方{ない}、戦い{だ}！</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What a shame.
+Then I suppose there's no other choice... Let's fight! </t>
+  </si>
+  <si>
+    <t xml:space="preserve">{おお}、本当{か}？
+おかげで楽ができそう{だ}、助かる{よ}。
+{よし}、&lt;color=green&gt;#2&lt;/color&gt;を受け取って{くれ}。</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Oh, really?
+That makes things much easier for me. I appreciate it.
+Alright, take this </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">&lt;color=green&gt;#2&lt;/color&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">RQX_negoaccept,1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;color=green&gt;#2&lt;/color&gt;では足りないの{か}？がめつい{な}！
+わかった{よ}、&lt;color=green&gt;#3&lt;/color&gt;も付け{る}。
+{よし}、持っていき{なさい}！
+これ以上は無い{よ}！</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">&lt;color=green&gt;#2&lt;/color&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> isn't enough? You're pretty greedy!
+Fine, I'll throw in </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">&lt;color=green&gt;#3&lt;/color&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> as well.
+Alright, take it and go!
+That's the absolute most I'm willing to offer!</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">RQX_negoraise,1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{おや}、わかっていない{な}。
+寛大にも{I}が{YOU}を見逃して、しかも金もやると言っているの{だが}。
+人の好意を素直に受け取らない奴は痛い目にあってもらう{よ}！</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oh, you don't seem to understand.
+I'm being generous enough to let you go and even give you money on top of that.
+If you can't accept someone's kindness, then I'll have to teach you a painful lesson!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">assassin_TG_nonego_1_main</t>
+  </si>
+  <si>
+    <t xml:space="preserve">見つけた{よ}！&lt;color=green&gt;#1&lt;/color&gt;{だ}！</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Got 'em! It’s &lt;color=green&gt;#1&lt;/color&gt;!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{おや}…護衛に雇われた冒険者{か}？
+悪い{が}、邪魔者には消えてもらう{よ}！</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oh my... An adventurer hired as a bodyguard, huh?
+Sorry, but I’ll have to get rid of anyone who gets in my way!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">assassin_TG_nego_1_main</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ちょっと待った！</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WAIT!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;color=green&gt;#1&lt;/color&gt;の護衛{か}？
+何故護衛しているかまでは詮索しない{が}、
+そいつはロクな奴では{ない}。
+善行だと思って、ここは{I}に引き渡してくれない{か}？
+一応礼もする{よ}、&lt;color=green&gt;#2&lt;/color&gt;を払{う}。どう{だ}？</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Are you escorting </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">&lt;color=green&gt;#1&lt;/color&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">?
+I won't pry into why you're protecting them, but that person is no good.
+Think of it as doing the right thing and hand them over to me.
+I'll even reward you for it. I'll pay you </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">&lt;color=green&gt;#2&lt;/color&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.
+How about it?</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">assassin_TG_nego_1_refuse</t>
+  </si>
+  <si>
+    <t xml:space="preserve">assassin_TG_nego_1_accept</t>
+  </si>
+  <si>
+    <t xml:space="preserve">assassin_TG_nego_1_raise</t>
+  </si>
+  <si>
+    <t xml:space="preserve">assassin_TG_nego_1_bust</t>
+  </si>
+  <si>
+    <t xml:space="preserve">そう{か}。それなら、実力行使といく{よ}！</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I SEE. In that case, I'll have to use force! </t>
+  </si>
+  <si>
+    <t xml:space="preserve">{よし}、それでいい{のだ}。
+ほら、約束の&lt;color=green&gt;#2&lt;/color&gt;{だ}。
+{YOU}、これからはこういう依頼には関わらないこと{だな}。</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Good, that's the right choice.
+Here, take the </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">&lt;color=green&gt;#2&lt;/color&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> I promised you.
+You should stay away from jobs like this from now on.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">{おお}…。
+しょうがない{な}、&lt;color=green&gt;#3&lt;/color&gt;も{だ}。
+言っておく{が}、これが限度{だよ}！{さようなら}！</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Damn...
+Fine, I'll add another </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">&lt;color=green&gt;#3&lt;/color&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.
+But I'm warning you, this is my final offer! Period!</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">ん…？もしかして話が通じない手合い{か}？
+なら、{I}が間違っていた{か}。
+話が通じない相手には交渉は無意味{だな}！</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hmm...? Are you the kind of person who can't be reasoned with?
+Then perhaps I was mistaken.
+There's no point negotiating with someone who won't listen!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">brigand_TG_nonego_1_main</t>
+  </si>
+  <si>
+    <t xml:space="preserve">おい！そこの{YOU}！</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oi! You there!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">なかなかいい武器を持っている{な}！
+おっと、売ってくれと頼むわけでは{ない}。
+…死体から盗むほうがずっと簡単だからな！ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">You’ve got some really shiny weapons there!
+Whoa, I’m not asking you to sell it to me.
+You'll be so much easier to rob when you're dead…</t>
+  </si>
+  <si>
+    <t xml:space="preserve">brigand_TG_nego_1_main</t>
+  </si>
+  <si>
+    <t xml:space="preserve">おい、そこの。ちょっと待って{くれ}。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hey, yer there. Wait a minute.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">それは&lt;color=green&gt;#1&lt;/color&gt;じゃない{か}？
+どうして{YOU}が持っている{のだ}？
+そいつはガード達が血眼になって探している物{だよ}？
+事を荒立てる前に、こっちに渡してくれない{か}？
+もちろんタダとは言わない{よ}、&lt;color=green&gt;#2&lt;/color&gt;でどう{だ}？</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Isn't that a </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">&lt;color=green&gt;#1&lt;/color&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">?
+Why do you have it?
+The guards have been searching everywhere for that thing.
+Before this turns into a bigger issue, could you hand it over to me?
+Of course, I won't ask you to do it for free.
+How does </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">&lt;color=green&gt;#2&lt;/color&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> sound?</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">brigand_TG_nego_1_refuse</t>
+  </si>
+  <si>
+    <t xml:space="preserve">brigand_TG_nego_1_accept</t>
+  </si>
+  <si>
+    <t xml:space="preserve">brigand_TG_nego_1_raise</t>
+  </si>
+  <si>
+    <t xml:space="preserve">brigand_TG_nego_1_bust</t>
+  </si>
+  <si>
+    <t xml:space="preserve">やはり、渡す気は無い{か}。 
+では、奪うのみ{だ}！</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I kind of had a feeling you wouldn't give it to me, after all.
+Then, I’ll just have to take it!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">話が早くて助かる{よ}。{ありがとう}！</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I'm glad you understand. That makes things much easier. Thanks! </t>
+  </si>
+  <si>
+    <t xml:space="preserve">下手に出ればいい気になって…！
+では、&lt;color=green&gt;#3&lt;/color&gt;も出す{よ}。
+これでいい{な}？では、{さようなら}！</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">I try to be reasonable, and you start taking advantage of it...!
+Fine, I'll throw in another </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">&lt;color=green&gt;#3&lt;/color&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.
+That should be enough, right? Now, goodbye!</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">だめ{だ}。これ以上は出さない。
+{YOU}が不服なら、交渉決裂{だな}。
+力づくでいかせてもらう{よ}！</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No chance. I'm not giving any more.
+You're not satisfied with that, then the negotiations are OFF.
+I'll just have to take it by force!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rescue_common_thank1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">助かった{よ}！{ありがとう}！</t>
+  </si>
+  <si>
+    <t xml:space="preserve">You are my savior! Thank you very much!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{よし}、後は{I}を&lt;color=green&gt;#1&lt;/color&gt;まで連れていって{くれ}。
+{たのむ}！</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Okay, now take me to &lt;color=green&gt;#1&lt;/color&gt;.
+Please!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">doggohint_FG_1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ひ、人殺し{だ}！誰か助けて{くれ}！</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M— Murderer! Somebody, HELP!
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">誰か！あの&lt;color=red&gt;マスク&lt;/color&gt;の奴を…
+ぬわーーっっ！！</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anyone at all! Stop that &lt;color=red&gt;masked&lt;/color&gt;… Aaaargh!!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">refAction1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">refAction2</t>
   </si>
 </sst>
 </file>
@@ -99,7 +733,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -124,6 +758,13 @@
       <name val="Arial"/>
       <family val="0"/>
       <charset val="128"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -174,7 +815,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -187,8 +828,20 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -374,17 +1027,18 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:K17"/>
+  <dimension ref="A1:L124"/>
   <sheetFormatPr defaultColWidth="9.0546875" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="21.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="1" width="8.84"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="11.84"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="16.12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="8.84"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="1" width="7.5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="42.13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="53.27"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="27.87"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="25.87"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="12.84"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="1" width="11.84"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="16.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="8.84"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="8" style="1" width="7.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="62.23"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="53.27"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -418,82 +1072,989 @@
       <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
+      <c r="L1" s="2" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H2" s="1" t="n">
-        <f aca="false">MAX(H4:H1048576)</f>
-        <v>2</v>
+      <c r="I2" s="1" t="n">
+        <f aca="false">MAX(I4:I1048576)</f>
+        <v>41</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D5" s="1" t="s">
-        <v>11</v>
+      <c r="E5" s="1" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D6" s="1" t="s">
-        <v>12</v>
+      <c r="E6" s="1" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H12" s="1" t="n">
+      <c r="I12" s="1" t="n">
         <v>1</v>
-      </c>
-      <c r="I12" s="1" t="s">
-        <v>15</v>
       </c>
       <c r="J12" s="1" t="s">
         <v>16</v>
       </c>
+      <c r="K12" s="3" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="I15" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="J15" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K15" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I16" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="J16" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="K16" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E17" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E18" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B19" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="I21" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="J21" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K21" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I22" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="J22" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="K22" s="4" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B23" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="I23" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="J23" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="K23" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B24" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="I24" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="J24" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="K24" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B25" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="I25" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="J25" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="K25" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B26" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="I26" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="J26" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="K26" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="I28" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="J28" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="K28" s="5" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E29" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E30" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B31" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="I33" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="J33" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="K33" s="5" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E34" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E35" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B36" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="I38" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="J38" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="K38" s="4" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E39" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F39" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E40" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F40" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B41" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="I43" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="J43" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="K43" s="5" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E44" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F44" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E45" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F45" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B46" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="I48" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="J48" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="K48" s="3" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I49" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="J49" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="K49" s="5" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E50" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F50" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E51" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F51" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B52" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="I54" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="J54" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="K54" s="5" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I55" s="1" t="n">
         <v>17</v>
       </c>
-    </row>
-    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="1" t="s">
+      <c r="J55" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="K55" s="5" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B56" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="E56" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="I56" s="1" t="n">
         <v>18</v>
       </c>
-    </row>
-    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H15" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="I15" s="1" t="s">
+      <c r="J56" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="K56" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B57" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="E57" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="I57" s="1" t="n">
         <v>19</v>
       </c>
-      <c r="J15" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H16" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="I16" s="3" t="s">
+      <c r="J57" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="K57" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B58" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E58" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="I58" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="J16" s="3" t="s">
+      <c r="J58" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="K58" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B59" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E59" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="I59" s="1" t="n">
         <v>21</v>
       </c>
-    </row>
-    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="1" t="s">
-        <v>17</v>
+      <c r="J59" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="K59" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="I61" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="J61" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="K61" s="3" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E62" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F62" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E63" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F63" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B64" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="I66" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="J66" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="K66" s="5" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E67" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F67" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E68" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F68" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B69" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="71" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A71" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="I71" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="J71" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="K71" s="5" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E72" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F72" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E73" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F73" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B74" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="76" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A76" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="I76" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="J76" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="K76" s="5" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E77" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F77" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E78" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F78" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B79" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A81" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="I81" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="J81" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="K81" s="3" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="82" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I82" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="J82" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="K82" s="5" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E83" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F83" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E84" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F84" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B85" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A87" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="I87" s="1" t="n">
+        <v>28</v>
+      </c>
+      <c r="J87" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="K87" s="3" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="88" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I88" s="1" t="n">
+        <v>29</v>
+      </c>
+      <c r="J88" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="K88" s="5" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B89" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="E89" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="I89" s="1" t="n">
+        <v>30</v>
+      </c>
+      <c r="J89" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="K89" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="90" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B90" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="E90" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="I90" s="1" t="n">
+        <v>31</v>
+      </c>
+      <c r="J90" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="K90" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B91" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C91" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E91" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="I91" s="1" t="n">
+        <v>32</v>
+      </c>
+      <c r="J91" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="K91" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="92" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B92" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="C92" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E92" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="I92" s="1" t="n">
+        <v>33</v>
+      </c>
+      <c r="J92" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="K92" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="94" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A94" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="I94" s="1" t="n">
+        <v>34</v>
+      </c>
+      <c r="J94" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="K94" s="5" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="95" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E95" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F95" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="96" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E96" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F96" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="97" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B97" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="99" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A99" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="I99" s="1" t="n">
+        <v>35</v>
+      </c>
+      <c r="J99" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="K99" s="3" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="100" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E100" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F100" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="101" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E101" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F101" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="102" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B102" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="104" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A104" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="I104" s="1" t="n">
+        <v>36</v>
+      </c>
+      <c r="J104" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="K104" s="5" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="105" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E105" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F105" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="106" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E106" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F106" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="107" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B107" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="109" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A109" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="I109" s="1" t="n">
+        <v>37</v>
+      </c>
+      <c r="J109" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="K109" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="110" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E110" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F110" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="111" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E111" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F111" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="112" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B112" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="113" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J113" s="4"/>
+    </row>
+    <row r="114" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A114" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="I114" s="1" t="n">
+        <v>38</v>
+      </c>
+      <c r="J114" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="K114" s="3" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="115" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I115" s="1" t="n">
+        <v>39</v>
+      </c>
+      <c r="J115" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="K115" s="5" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="116" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B116" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="118" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A118" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="I118" s="1" t="n">
+        <v>40</v>
+      </c>
+      <c r="J118" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="K118" s="5" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="119" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I119" s="1" t="n">
+        <v>41</v>
+      </c>
+      <c r="J119" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="K119" s="3" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="120" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B120" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="122" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A122" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E122" s="4" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="123" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E123" s="4" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="124" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B124" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
   </sheetData>
